--- a/framework-templates/registers/Financial_Promotions_Log_v2.0_Template.xlsx
+++ b/framework-templates/registers/Financial_Promotions_Log_v2.0_Template.xlsx
@@ -8,12 +8,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Promotions Log" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approval Checklist" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Financial Promotions Log'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Approval Checklist'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -150,7 +148,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -186,6 +184,50 @@
       <bottom style="thin">
         <color rgb="00A6A6A6"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -667,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -701,73 +743,45 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>Yellow cells containing text in [square brackets] are placeholders – replace them with your own details. Green header cells are column headings; do not delete a column unless the guidance for that column says you may.</t>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>This register</t>
         </is>
       </c>
     </row>
     <row r="7" ht="49" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>Green “OPTION” rows mark rows that only apply to particular regulated activities. Keep the rows under an OPTION label if your firm carries on that activity; otherwise delete the OPTION row and the rows beneath it, down to the next OPTION row. Each option stands alone.</t>
+          <t>One line for every financial promotion (and version) approved, including social media posts, influencer and affiliate content, and scripts for real-time promotions. Nothing is published until it has been approved and logged. Keep a copy of each promotion exactly as it appeared, its approval, the evidence for its claims and when it was withdrawn.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
+          <t>Yellow cells containing text in [square brackets] are placeholders – replace them with your own details. Green header cells are column headings; do not delete a column unless the guidance for that column says you may.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="49" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>Green “OPTION” rows mark rows that only apply to particular regulated activities. Keep the rows under an OPTION label if your firm carries on that activity; otherwise delete the OPTION row and the rows beneath it, down to the next OPTION row. Each option stands alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
           <t>Drop-down lists are provided for consistency. The underlying lists are on a hidden sheet called “Lists” – unhide it (right-click any sheet tab, Unhide) if you need to change them.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Keep this register securely, restrict access to the people who need it, and keep it for the retention period set out in the relevant policy and your Data Retention Schedule.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>What this workbook contains</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="49" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>1. Financial Promotions Log – one line for every financial promotion (and version) approved, including social media posts, influencer and affiliate content, and scripts for real-time promotions. This is the “Financial Promotions Log” referred to in the Financial Promotions Policy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>2. Approval Checklist – complete a copy for each promotion before approval. This is the “Financial Promotion Checklist” referred to in the policy. Keep the completed checklist with the promotion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>Records</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>Keep a copy of each promotion exactly as it appeared (screenshots for social media), its approval, the evidence for its claims (for example the basis of a representative APR), and when it was withdrawn, for at least [Insert period].</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>Regulatory watch – not yet final: The DMCC Act 2024 subscription contracts regime is now expected to commence in spring 2027 and will affect promotions of subscription services.</t>
         </is>
       </c>
     </row>
@@ -4713,800 +4727,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D58"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>Financial Promotion Approval Checklist</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>Promotion ref.: [Insert]   |   Approver: [Insert name]   |   Date: [Insert date]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="19" customHeight="1">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>KMS guidance: Complete before approving any promotion. Every applicable check must be “Yes” before approval.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="C4" s="21" t="inlineStr">
-        <is>
-          <t>Met? (Yes / No / N/A)</t>
-        </is>
-      </c>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t>Comments / changes required</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>Is it a promotion?</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>The communication is (or contains) an invitation or inducement to engage in investment activity, or is a customer communication that must still be clear, fair and not misleading.</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="22" t="n"/>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
-        <is>
-          <t>Section 21</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>We are permitted to communicate / approve it; if approving for an unauthorised person, we hold the s21 approver permission or an exemption applies.</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="n"/>
-      <c r="D6" s="22" t="n"/>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
-        <is>
-          <t>Target audience</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>Target audience identified and consistent with the product’s target market; not aimed at customers likely to be harmed.</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
-        <is>
-          <t>Fair, clear, not misleading</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>Accurate, evidenced and balanced; benefits not emphasised without equally prominent risks, costs and limitations.</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="22" t="n"/>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="22" t="inlineStr">
-        <is>
-          <t>Prominence</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>Required information and warnings are prominent and in the promotion itself (not only behind a link or in a comment).</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="n"/>
-      <c r="D9" s="22" t="n"/>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
-        <is>
-          <t>Plain language</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>Plain English; technical terms explained; suitable for customers with characteristics of vulnerability.</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n"/>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
-        <is>
-          <t>No pressure</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>No false urgency, countdown timers or exploitation of behavioural biases.</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="n"/>
-      <c r="D11" s="22" t="n"/>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
-        <is>
-          <t>Firm identified</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>Firm name and, where required, FCA status shown.</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="n"/>
-      <c r="D12" s="22" t="n"/>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t>Channel rules</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>Meets the channel standards in the policy (e.g. FG24/1 for social media: each post compliant on its own; adverts labelled).</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="n"/>
-      <c r="D13" s="22" t="n"/>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
-        <is>
-          <t>Consumer Duty</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
-        <is>
-          <t>Supports consumer understanding (PRIN 2A.5) and is consistent with the product’s fair value assessment.</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="22" t="n"/>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="22" t="inlineStr">
-        <is>
-          <t>Records</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>Final version, evidence and approval saved; entered in the Financial Promotions Log with review date.</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="n"/>
-      <c r="D15" s="22" t="n"/>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>OPTION – Credit broking firms   [Keep the rows below, down to the next OPTION row, only if your firm carries on credit broking. Otherwise delete them.]</t>
-        </is>
-      </c>
-      <c r="B16" s="25" t="n"/>
-      <c r="C16" s="25" t="n"/>
-      <c r="D16" s="25" t="n"/>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>Broker status shown: we are a credit broker, not a lender; extent of lender panel; any fee disclosed (CONC 3).</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="22" t="n"/>
-    </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>Representative example included, and more prominent than the trigger, where a rate or cost figure is shown; representative APR meets the 51% test and evidence is on file (CONC 3.5).</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="n"/>
-      <c r="D18" s="22" t="n"/>
-    </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>No “pre-approved”, “guaranteed” or “regardless of credit history” claims; HCSTC risk warning included if applicable.</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="n"/>
-      <c r="D19" s="22" t="n"/>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
-        <is>
-          <t>OPTION – Debt adjusting and debt counselling firms   [Keep the rows below, down to the next OPTION row, only if your firm carries on debt adjusting and/or debt counselling. Otherwise delete them.]</t>
-        </is>
-      </c>
-      <c r="B20" s="25" t="n"/>
-      <c r="C20" s="25" t="n"/>
-      <c r="D20" s="25" t="n"/>
-    </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t>States that free debt advice is available and how to find it (e.g. MoneyHelper).</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="22" t="n"/>
-    </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B22" s="22" t="inlineStr">
-        <is>
-          <t>No misleading claims that debts will be written off, that the solution is government-backed or free.</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="n"/>
-      <c r="D22" s="22" t="n"/>
-    </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="inlineStr">
-        <is>
-          <t>Fees disclosed clearly; lead source authorised and checked.</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="22" t="n"/>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
-        <is>
-          <t>OPTION – Debt collecting and debt administration firms   [Keep the rows below, down to the next OPTION row, only if your firm carries on debt collecting and/or debt administration. Otherwise delete them.]</t>
-        </is>
-      </c>
-      <c r="B24" s="25" t="n"/>
-      <c r="C24" s="25" t="n"/>
-      <c r="D24" s="25" t="n"/>
-    </row>
-    <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="inlineStr">
-        <is>
-          <t>Collection communication does not misrepresent authority or legal position, or threaten action we cannot or will not take (CONC 7).</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="22" t="n"/>
-    </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B26" s="22" t="inlineStr">
-        <is>
-          <t>Signposts free debt advice.</t>
-        </is>
-      </c>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="22" t="n"/>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
-        <is>
-          <t>OPTION – Credit information services and credit references firms   [Keep the rows below, down to the next OPTION row, only if your firm provides credit information services and/or credit references. Otherwise delete them.]</t>
-        </is>
-      </c>
-      <c r="B27" s="25" t="n"/>
-      <c r="C27" s="25" t="n"/>
-      <c r="D27" s="25" t="n"/>
-    </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B28" s="22" t="inlineStr">
-        <is>
-          <t>Does not overstate what the service can do (e.g. “fix your credit score”).</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="n"/>
-      <c r="D28" s="22" t="n"/>
-    </row>
-    <row r="29" ht="36" customHeight="1">
-      <c r="A29" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B29" s="22" t="inlineStr">
-        <is>
-          <t>Statutory free access made clear; free trial / subscription price, start date and cancellation shown with equal prominence.</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="n"/>
-      <c r="D29" s="22" t="n"/>
-    </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
-        <is>
-          <t>OPTION – Peer-to-peer lending platforms firms   [Keep the rows below, down to the next OPTION row, only if your firm operates an electronic system in relation to lending. Otherwise delete them.]</t>
-        </is>
-      </c>
-      <c r="B30" s="25" t="n"/>
-      <c r="C30" s="25" t="n"/>
-      <c r="D30" s="25" t="n"/>
-    </row>
-    <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B31" s="22" t="inlineStr">
-        <is>
-          <t>Prescribed restricted mass market investment risk warning included and prominent, with link to risk summary (COBS 4.12A).</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="22" t="n"/>
-    </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B32" s="22" t="inlineStr">
-        <is>
-          <t>No incentives to invest; audience restricted to categorised investors; direct offer promotions only after appropriateness, with 24-hour cooling-off and personalised risk warning.</t>
-        </is>
-      </c>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="22" t="n"/>
-    </row>
-    <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B33" s="22" t="inlineStr">
-        <is>
-          <t>Borrower promotions: CONC 3 representative example where a rate or cost is shown.</t>
-        </is>
-      </c>
-      <c r="C33" s="22" t="n"/>
-      <c r="D33" s="22" t="n"/>
-    </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="24" t="inlineStr">
-        <is>
-          <t>OPTION – Consumer credit lending firms   [Keep the rows below, down to the next OPTION row, only if your firm enters into regulated credit agreements as lender. Otherwise delete them.]</t>
-        </is>
-      </c>
-      <c r="B34" s="25" t="n"/>
-      <c r="C34" s="25" t="n"/>
-      <c r="D34" s="25" t="n"/>
-    </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B35" s="22" t="inlineStr">
-        <is>
-          <t>Representative example included where a rate or cost figure is shown; representative APR meets the 51% test and evidence is on file (CONC 3.5).</t>
-        </is>
-      </c>
-      <c r="C35" s="22" t="n"/>
-      <c r="D35" s="22" t="n"/>
-    </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B36" s="22" t="inlineStr">
-        <is>
-          <t>No “pre-approved” or “regardless of credit history” claims; HCSTC risk warning if applicable; deferred payment credit not presented as risk-free.</t>
-        </is>
-      </c>
-      <c r="C36" s="22" t="n"/>
-      <c r="D36" s="22" t="n"/>
-    </row>
-    <row r="37" ht="36" customHeight="1">
-      <c r="A37" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B37" s="22" t="inlineStr">
-        <is>
-          <t>Promotions communicated by brokers / merchants: approved content only; s21 approver regime position checked.</t>
-        </is>
-      </c>
-      <c r="C37" s="22" t="n"/>
-      <c r="D37" s="22" t="n"/>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="24" t="inlineStr">
-        <is>
-          <t>OPTION – Exercising a lender’s rights and duties firms   [Keep the rows below, down to the next OPTION row, only if your firm exercises the lender’s rights and duties under regulated credit agreements. Otherwise delete them.]</t>
-        </is>
-      </c>
-      <c r="B38" s="25" t="n"/>
-      <c r="C38" s="25" t="n"/>
-      <c r="D38" s="25" t="n"/>
-    </row>
-    <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B39" s="22" t="inlineStr">
-        <is>
-          <t>Settlement or arrangement offers clear on terms and credit file effect; no false urgency.</t>
-        </is>
-      </c>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="22" t="n"/>
-    </row>
-    <row r="40" ht="36" customHeight="1">
-      <c r="A40" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B40" s="22" t="inlineStr">
-        <is>
-          <t>Communication clear about who we are; does not misrepresent legal position (CONC 7).</t>
-        </is>
-      </c>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="22" t="n"/>
-    </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="24" t="inlineStr">
-        <is>
-          <t>OPTION – Consumer hire firms   [Keep the rows below, down to the next OPTION row, only if your firm hires out goods under regulated consumer hire agreements. Otherwise delete them.]</t>
-        </is>
-      </c>
-      <c r="B41" s="25" t="n"/>
-      <c r="C41" s="25" t="n"/>
-      <c r="D41" s="25" t="n"/>
-    </row>
-    <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B42" s="22" t="inlineStr">
-        <is>
-          <t>States the customer will not own the goods; total cost, hire period and end-of-hire / damage / excess charges shown fairly (CONC 3).</t>
-        </is>
-      </c>
-      <c r="C42" s="22" t="n"/>
-      <c r="D42" s="22" t="n"/>
-    </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="24" t="inlineStr">
-        <is>
-          <t>OPTION – Insurance distribution firms   [Keep the rows below, down to the next OPTION row, only if your firm carries on insurance distribution. Otherwise delete them.]</t>
-        </is>
-      </c>
-      <c r="B43" s="25" t="n"/>
-      <c r="C43" s="25" t="n"/>
-      <c r="D43" s="25" t="n"/>
-    </row>
-    <row r="44" ht="36" customHeight="1">
-      <c r="A44" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B44" s="22" t="inlineStr">
-        <is>
-          <t>Cover, key exclusions and limitations presented fairly (ICOBS 2.2).</t>
-        </is>
-      </c>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="22" t="n"/>
-    </row>
-    <row r="45" ht="36" customHeight="1">
-      <c r="A45" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B45" s="22" t="inlineStr">
-        <is>
-          <t>“From £x” prices achievable by a meaningful proportion of customers; comparisons fair.</t>
-        </is>
-      </c>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="22" t="n"/>
-    </row>
-    <row r="46" ht="36" customHeight="1">
-      <c r="A46" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B46" s="22" t="inlineStr">
-        <is>
-          <t>Home / motor: consistent with pricing practices rules (ICOBS 6B); add-ons not presented as compulsory.</t>
-        </is>
-      </c>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="22" t="n"/>
-    </row>
-    <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="24" t="inlineStr">
-        <is>
-          <t>OPTION – Mortgage intermediation firms   [Keep the rows below, down to the next OPTION row, only if your firm advises on and/or arranges regulated mortgage contracts. Otherwise delete them.]</t>
-        </is>
-      </c>
-      <c r="B47" s="25" t="n"/>
-      <c r="C47" s="25" t="n"/>
-      <c r="D47" s="25" t="n"/>
-    </row>
-    <row r="48" ht="36" customHeight="1">
-      <c r="A48" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B48" s="22" t="inlineStr">
-        <is>
-          <t>Repossession risk warning included (and debt consolidation warning if applicable) (MCOB 3A).</t>
-        </is>
-      </c>
-      <c r="C48" s="22" t="n"/>
-      <c r="D48" s="22" t="n"/>
-    </row>
-    <row r="49" ht="36" customHeight="1">
-      <c r="A49" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B49" s="22" t="inlineStr">
-        <is>
-          <t>Representative example with APRC where a rate or cost figure is shown (MCOB 3A).</t>
-        </is>
-      </c>
-      <c r="C49" s="22" t="n"/>
-      <c r="D49" s="22" t="n"/>
-    </row>
-    <row r="50" ht="36" customHeight="1">
-      <c r="A50" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B50" s="22" t="inlineStr">
-        <is>
-          <t>Fee and whole-of-market / limited panel status stated.</t>
-        </is>
-      </c>
-      <c r="C50" s="22" t="n"/>
-      <c r="D50" s="22" t="n"/>
-    </row>
-    <row r="51" ht="32" customHeight="1">
-      <c r="A51" s="24" t="inlineStr">
-        <is>
-          <t>OPTION – Payment services and e-money firms   [Keep the rows below, down to the next OPTION row, only if your firm provides payment services or issues electronic money. Otherwise delete them.]</t>
-        </is>
-      </c>
-      <c r="B51" s="25" t="n"/>
-      <c r="C51" s="25" t="n"/>
-      <c r="D51" s="25" t="n"/>
-    </row>
-    <row r="52" ht="36" customHeight="1">
-      <c r="A52" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B52" s="22" t="inlineStr">
-        <is>
-          <t>Does not call e-money or safeguarded funds a deposit or bank account, or imply FSCS protection.</t>
-        </is>
-      </c>
-      <c r="C52" s="22" t="n"/>
-      <c r="D52" s="22" t="n"/>
-    </row>
-    <row r="53" ht="36" customHeight="1">
-      <c r="A53" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B53" s="22" t="inlineStr">
-        <is>
-          <t>Fees and exchange rates (including mark-ups) shown clearly; speed and security not overstated.</t>
-        </is>
-      </c>
-      <c r="C53" s="22" t="n"/>
-      <c r="D53" s="22" t="n"/>
-    </row>
-    <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="24" t="inlineStr">
-        <is>
-          <t>OPTION – Investment advice and arranging firms   [Keep the rows below, down to the next OPTION row, only if your firm advises on and/or arranges deals in investments. Otherwise delete them.]</t>
-        </is>
-      </c>
-      <c r="B54" s="25" t="n"/>
-      <c r="C54" s="25" t="n"/>
-      <c r="D54" s="25" t="n"/>
-    </row>
-    <row r="55" ht="36" customHeight="1">
-      <c r="A55" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B55" s="22" t="inlineStr">
-        <is>
-          <t>Fair, clear and not misleading with prominent risks; past / future performance and comparison rules met (COBS 4).</t>
-        </is>
-      </c>
-      <c r="C55" s="22" t="n"/>
-      <c r="D55" s="22" t="n"/>
-    </row>
-    <row r="56" ht="36" customHeight="1">
-      <c r="A56" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B56" s="22" t="inlineStr">
-        <is>
-          <t>High-risk investment restrictions and prescribed risk warnings met (COBS 4.12A / 4.12B) if applicable.</t>
-        </is>
-      </c>
-      <c r="C56" s="22" t="n"/>
-      <c r="D56" s="22" t="n"/>
-    </row>
-    <row r="57" ht="36" customHeight="1">
-      <c r="A57" s="22" t="inlineStr">
-        <is>
-          <t>Activity rules</t>
-        </is>
-      </c>
-      <c r="B57" s="22" t="inlineStr">
-        <is>
-          <t>Nature of service (independent / restricted) and charges stated.</t>
-        </is>
-      </c>
-      <c r="C57" s="22" t="n"/>
-      <c r="D57" s="22" t="n"/>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="26" t="inlineStr">
-        <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="B58" s="26" t="inlineStr">
-        <is>
-          <t>Approved / rejected: [Insert]   Approver signature: [Insert]</t>
-        </is>
-      </c>
-      <c r="C58" s="26" t="n"/>
-      <c r="D58" s="26" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="A51:D51"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="C5:C58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Please choose a value from the list." type="list">
-      <formula1>Lists!$D$2:$D$4</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E14"/>
